--- a/data/trans_dic/P15D$consultar-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P15D$consultar-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuya consecuencia del último accidente fue, al menos, consultar con un profesional sanitario (fuera de un hospital)</t>
+          <t>Población cuya consecuencia del último accidente fue, al menos, consultar con un profesional sanitario (fuera de un hospital) (tasa de respuesta: 89,03%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,63; 39,51</t>
+          <t>4,91; 41,87</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,62</t>
+          <t>0,0; 8,89</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,78; 20,88</t>
+          <t>3,95; 21,24</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,49; 24,4</t>
+          <t>5,14; 24,47</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,01</t>
+          <t>0,0; 32,22</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,94; 18,54</t>
+          <t>1,96; 17,51</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,21; 26,27</t>
+          <t>6,39; 26,75</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9,6; 29,58</t>
+          <t>9,89; 29,27</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,3; 31,09</t>
+          <t>5,45; 29,25</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,77; 10,05</t>
+          <t>1,78; 9,84</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7,66; 20,49</t>
+          <t>6,94; 19,99</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,95; 22,22</t>
+          <t>8,77; 22,0</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,3; 22,76</t>
+          <t>4,24; 22,92</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,61; 17,67</t>
+          <t>2,95; 16,21</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,78; 25,51</t>
+          <t>7,55; 26,74</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,4; 18,85</t>
+          <t>3,82; 20,89</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,64; 33,85</t>
+          <t>3,63; 33,46</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,5; 21,62</t>
+          <t>5,52; 20,41</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,54; 26,61</t>
+          <t>5,37; 28,6</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,9; 25,36</t>
+          <t>9,33; 25,55</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,26; 21,49</t>
+          <t>6,7; 22,56</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5,45; 14,92</t>
+          <t>5,76; 15,64</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8,05; 21,65</t>
+          <t>8,57; 21,79</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,87; 19,3</t>
+          <t>8,24; 19,76</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,67; 47,39</t>
+          <t>8,49; 43,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,4; 20,6</t>
+          <t>4,01; 22,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,79</t>
+          <t>0,0; 16,33</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,74</t>
+          <t>0,0; 15,43</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,15</t>
+          <t>0,0; 22,46</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,61</t>
+          <t>0,0; 8,64</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 6,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>14,26; 34,71</t>
+          <t>14,27; 36,65</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,36; 28,01</t>
+          <t>6,11; 29,27</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,53; 11,91</t>
+          <t>2,48; 11,66</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,14</t>
+          <t>0,0; 10,3</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9,71; 24,69</t>
+          <t>9,25; 24,47</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,86</t>
+          <t>0,0; 16,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,19; 19,78</t>
+          <t>5,2; 18,92</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,21; 28,31</t>
+          <t>8,54; 27,53</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,61; 23,26</t>
+          <t>1,64; 25,15</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,61; 44,57</t>
+          <t>4,63; 42,34</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,98; 21,64</t>
+          <t>5,38; 22,05</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,27; 20,31</t>
+          <t>3,29; 19,61</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,78; 27,85</t>
+          <t>10,87; 27,92</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,45; 22,68</t>
+          <t>4,08; 21,51</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6,84; 18,29</t>
+          <t>6,81; 17,8</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8,43; 21,16</t>
+          <t>8,41; 20,65</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>8,05; 20,6</t>
+          <t>7,97; 21,19</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,3; 20,55</t>
+          <t>8,14; 20,21</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,43; 11,82</t>
+          <t>5,15; 11,91</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,44; 18,12</t>
+          <t>8,8; 18,1</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,08; 14,18</t>
+          <t>5,2; 14,62</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,93; 22,56</t>
+          <t>7,27; 21,86</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,48; 12,97</t>
+          <t>5,32; 12,35</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,21; 15,18</t>
+          <t>6,63; 15,73</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>14,27; 23,35</t>
+          <t>14,49; 23,91</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,19; 18,71</t>
+          <t>8,86; 18,51</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6,28; 11,4</t>
+          <t>6,03; 11,18</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8,54; 15,16</t>
+          <t>8,61; 14,69</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>10,86; 17,44</t>
+          <t>11,09; 17,28</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuya consecuencia del último accidente fue, al menos, consultar con un profesional sanitario (fuera de un hospital)</t>
+          <t>Población cuya consecuencia del último accidente fue, al menos, consultar con un profesional sanitario (fuera de un hospital) (tasa de respuesta: 89,03%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1055; 9002</t>
+          <t>1118; 9539</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 5090</t>
+          <t>0; 5250</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1574; 8687</t>
+          <t>1642; 8839</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2465; 10949</t>
+          <t>2306; 10981</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 5872</t>
+          <t>0; 5112</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1020; 9729</t>
+          <t>1027; 9188</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3021; 12785</t>
+          <t>3110; 13022</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4150; 12792</t>
+          <t>4276; 12656</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2820; 12017</t>
+          <t>2107; 11304</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1974; 11208</t>
+          <t>1989; 10969</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6915; 18499</t>
+          <t>6261; 18046</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>7888; 19585</t>
+          <t>7727; 19390</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1841; 9739</t>
+          <t>1814; 9807</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2853; 13970</t>
+          <t>2331; 12818</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4099; 15427</t>
+          <t>4565; 16171</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2277; 12640</t>
+          <t>2560; 14009</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1097; 10202</t>
+          <t>1094; 10085</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3991; 15686</t>
+          <t>4005; 14802</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2151; 12617</t>
+          <t>2547; 13560</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5666; 14513</t>
+          <t>5341; 14626</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4566; 15667</t>
+          <t>4886; 16446</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8265; 22618</t>
+          <t>8732; 23718</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8686; 23358</t>
+          <t>9243; 23503</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9787; 23987</t>
+          <t>10244; 24564</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2064; 11281</t>
+          <t>2022; 10428</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1954; 11839</t>
+          <t>2302; 12643</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 6155</t>
+          <t>0; 5987</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 5186</t>
+          <t>0; 4512</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 5101</t>
+          <t>0; 5415</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 4913</t>
+          <t>0; 4929</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 2074</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6290; 15310</t>
+          <t>6292; 16166</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3048; 13424</t>
+          <t>2928; 14025</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2893; 13642</t>
+          <t>2837; 13350</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 6235</t>
+          <t>0; 7027</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>7125; 18111</t>
+          <t>6785; 17944</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 6359</t>
+          <t>0; 5487</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4574; 17444</t>
+          <t>4591; 16687</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5605; 17240</t>
+          <t>5197; 16760</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>948; 13694</t>
+          <t>964; 14809</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1565; 10557</t>
+          <t>1097; 10031</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3602; 15641</t>
+          <t>3888; 15938</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2049; 12717</t>
+          <t>2060; 12277</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7441; 19225</t>
+          <t>7504; 19270</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2555; 13017</t>
+          <t>2342; 12347</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>10982; 29357</t>
+          <t>10928; 28565</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>10409; 26137</t>
+          <t>10381; 25503</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>10292; 26351</t>
+          <t>10192; 27107</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>10210; 25289</t>
+          <t>10013; 24879</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>15411; 33541</t>
+          <t>14609; 33785</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>16848; 36178</t>
+          <t>17558; 36131</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10158; 28360</t>
+          <t>10397; 29251</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>6496; 21166</t>
+          <t>6823; 20507</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13931; 32991</t>
+          <t>13536; 31420</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11817; 28885</t>
+          <t>12618; 29936</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>30477; 49877</t>
+          <t>30958; 51066</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>19934; 40590</t>
+          <t>19210; 40138</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>33805; 61371</t>
+          <t>32422; 60169</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>33298; 59107</t>
+          <t>33563; 57282</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>44914; 72141</t>
+          <t>45885; 71479</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P15D$consultar-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P15D$consultar-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,22%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,91; 41,87</t>
+          <t>4,62; 38,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,89</t>
+          <t>0,0; 8,64</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,95; 21,24</t>
+          <t>3,84; 22,12</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,14; 24,47</t>
+          <t>4,98; 24,12</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,22</t>
+          <t>0,0; 36,85</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,96; 17,51</t>
+          <t>1,9; 18,98</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,39; 26,75</t>
+          <t>5,82; 27,11</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9,89; 29,27</t>
+          <t>8,99; 28,33</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,45; 29,25</t>
+          <t>6,14; 29,88</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,78; 9,84</t>
+          <t>1,72; 9,77</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6,94; 19,99</t>
+          <t>6,8; 19,04</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,77; 22,0</t>
+          <t>8,28; 22,14</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,33%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,24; 22,92</t>
+          <t>4,27; 23,55</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,95; 16,21</t>
+          <t>2,86; 16,21</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,55; 26,74</t>
+          <t>6,94; 25,03</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,82; 20,89</t>
+          <t>3,58; 17,53</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,63; 33,46</t>
+          <t>4,05; 30,12</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,52; 20,41</t>
+          <t>5,53; 21,2</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,37; 28,6</t>
+          <t>4,72; 25,93</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,33; 25,55</t>
+          <t>9,93; 26,34</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,7; 22,56</t>
+          <t>6,29; 22,02</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5,76; 15,64</t>
+          <t>5,48; 15,23</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8,57; 21,79</t>
+          <t>8,35; 21,16</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,24; 19,76</t>
+          <t>7,72; 17,69</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,87%</t>
         </is>
       </c>
     </row>
@@ -997,32 +997,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,49; 43,8</t>
+          <t>8,25; 47,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,01; 22,0</t>
+          <t>3,82; 21,36</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,33</t>
+          <t>0,0; 16,96</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,43</t>
+          <t>0,0; 17,94</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,46</t>
+          <t>0,0; 18,46</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,64</t>
+          <t>0,0; 8,69</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1032,27 +1032,27 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>14,27; 36,65</t>
+          <t>14,3; 34,78</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,11; 29,27</t>
+          <t>4,4; 26,49</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,48; 11,66</t>
+          <t>2,56; 11,8</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,3</t>
+          <t>0,0; 9,8</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9,25; 24,47</t>
+          <t>9,85; 24,28</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>12,67%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,28</t>
+          <t>0,0; 17,65</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,2; 18,92</t>
+          <t>5,4; 20,37</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,54; 27,53</t>
+          <t>8,09; 27,41</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,64; 25,15</t>
+          <t>1,49; 22,39</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,63; 42,34</t>
+          <t>5,44; 44,72</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,38; 22,05</t>
+          <t>5,66; 22,34</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,29; 19,61</t>
+          <t>3,32; 19,28</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,87; 27,92</t>
+          <t>10,45; 26,35</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,08; 21,51</t>
+          <t>4,29; 23,94</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6,81; 17,8</t>
+          <t>6,68; 17,36</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8,41; 20,65</t>
+          <t>8,05; 20,93</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>7,97; 21,19</t>
+          <t>7,9; 19,99</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,48%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,14; 20,21</t>
+          <t>7,87; 20,82</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,15; 11,91</t>
+          <t>5,12; 11,58</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,8; 18,1</t>
+          <t>8,81; 17,67</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,2; 14,62</t>
+          <t>5,09; 13,76</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,27; 21,86</t>
+          <t>6,55; 21,37</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,32; 12,35</t>
+          <t>5,49; 12,51</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,63; 15,73</t>
+          <t>6,09; 15,42</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>14,49; 23,91</t>
+          <t>14,24; 23,07</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8,86; 18,51</t>
+          <t>8,81; 17,68</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6,03; 11,18</t>
+          <t>6,21; 11,2</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8,61; 14,69</t>
+          <t>8,6; 15,22</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,09; 17,28</t>
+          <t>10,64; 16,99</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5403</t>
+          <t>5809</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7646</t>
+          <t>7934</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>13049</t>
+          <t>13743</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1118; 9539</t>
+          <t>1052; 8722</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 5250</t>
+          <t>0; 5101</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1642; 8839</t>
+          <t>1596; 9205</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2306; 10981</t>
+          <t>2474; 11988</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 5112</t>
+          <t>0; 5847</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1027; 9188</t>
+          <t>999; 9960</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3110; 13022</t>
+          <t>2834; 13195</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4276; 12656</t>
+          <t>4217; 13292</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2107; 11304</t>
+          <t>2375; 11549</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1989; 10969</t>
+          <t>1917; 10897</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6261; 18046</t>
+          <t>6139; 17191</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>7727; 19390</t>
+          <t>7995; 21394</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5979</t>
+          <t>6557</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>9411</t>
+          <t>10416</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>15390</t>
+          <t>16973</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1814; 9807</t>
+          <t>1825; 10075</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2331; 12818</t>
+          <t>2264; 12822</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4565; 16171</t>
+          <t>4198; 15140</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2560; 14009</t>
+          <t>2675; 13118</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1094; 10085</t>
+          <t>1220; 9078</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4005; 14802</t>
+          <t>4015; 15375</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2547; 13560</t>
+          <t>2236; 12295</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5341; 14626</t>
+          <t>6234; 16540</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4886; 16446</t>
+          <t>4586; 16059</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8732; 23718</t>
+          <t>8315; 23098</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9243; 23503</t>
+          <t>9006; 22826</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10244; 24564</t>
+          <t>10629; 24343</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1217</t>
+          <t>1843</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10356</t>
+          <t>11246</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11573</t>
+          <t>13089</t>
         </is>
       </c>
     </row>
@@ -2061,32 +2061,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2022; 10428</t>
+          <t>1963; 11194</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2302; 12643</t>
+          <t>2193; 12272</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 5987</t>
+          <t>0; 6218</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 4512</t>
+          <t>0; 5916</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 5415</t>
+          <t>0; 4452</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 4929</t>
+          <t>0; 4956</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -2096,27 +2096,27 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6292; 16166</t>
+          <t>7076; 17208</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2928; 14025</t>
+          <t>2111; 12692</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2837; 13350</t>
+          <t>2937; 13515</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 7027</t>
+          <t>0; 6685</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6785; 17944</t>
+          <t>8123; 20021</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4558</t>
+          <t>4638</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>12338</t>
+          <t>12658</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>16897</t>
+          <t>17296</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 5487</t>
+          <t>0; 5949</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4591; 16687</t>
+          <t>4763; 17970</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5197; 16760</t>
+          <t>4924; 16689</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>964; 14809</t>
+          <t>944; 14227</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1097; 10031</t>
+          <t>1289; 10595</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3888; 15938</t>
+          <t>4089; 16150</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2060; 12277</t>
+          <t>2082; 12071</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7504; 19270</t>
+          <t>7623; 19225</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2342; 12347</t>
+          <t>2462; 13740</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>10928; 28565</t>
+          <t>10727; 27858</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>10381; 25503</t>
+          <t>9942; 25852</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>10192; 27107</t>
+          <t>10780; 27291</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17157</t>
+          <t>18847</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>39751</t>
+          <t>42255</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>56908</t>
+          <t>61101</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>10013; 24879</t>
+          <t>9685; 25623</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>14609; 33785</t>
+          <t>14526; 32864</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>17558; 36131</t>
+          <t>17590; 35275</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10397; 29251</t>
+          <t>11255; 30416</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>6823; 20507</t>
+          <t>6149; 20042</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13536; 31420</t>
+          <t>13971; 31828</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12618; 29936</t>
+          <t>11592; 29343</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>30958; 51066</t>
+          <t>33063; 53568</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>19210; 40138</t>
+          <t>19114; 38341</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>32422; 60169</t>
+          <t>33423; 60281</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>33563; 57282</t>
+          <t>33532; 59360</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>45885; 71479</t>
+          <t>48231; 77018</t>
         </is>
       </c>
     </row>
